--- a/既成ファイル/取込_設定シート_修正後.xlsx
+++ b/既成ファイル/取込_設定シート_修正後.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>「YYYY年MM月DD日」→「YYYY-MM-DD」へ変換</t>
+          <t>日付は「YYYY-MM-DD」形式に正規化（「YYYY年MM月DD日」等の入力にも対応）</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>「YYYY年MM月DD日」→「YYYY-MM-DD」へ変換</t>
+          <t>日付は「YYYY-MM-DD」形式に正規化（「YYYY年MM月DD日」等の入力にも対応）</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>「YYYY年MM月DD日」→「YYYY-MM-DD」へ変換</t>
+          <t>日付は「YYYY-MM-DD」形式に正規化（「YYYY年MM月DD日」等の入力にも対応）</t>
         </is>
       </c>
     </row>
